--- a/datos_estandarizados.xlsx
+++ b/datos_estandarizados.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -86,8 +86,14 @@
       <color rgb="FF1E3A5F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -154,8 +160,13 @@
         <bgColor rgb="FFBBDEFB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3654"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border/>
     <border>
       <left style="thin">
@@ -216,11 +227,25 @@
         <color rgb="FF000000"/>
       </top>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -341,6 +366,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -617,7 +645,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.63" customWidth="1" style="44" min="1" max="1"/>
@@ -626,6 +654,8 @@
     <col width="11.5" customWidth="1" style="44" min="4" max="4"/>
     <col width="10.5" customWidth="1" style="44" min="5" max="5"/>
     <col width="12.63" customWidth="1" style="44" min="6" max="7"/>
+    <col width="60" customWidth="1" style="44" min="17" max="17"/>
+    <col width="55" customWidth="1" style="44" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="44">
@@ -760,6 +790,16 @@
           <t>Relevancia</t>
         </is>
       </c>
+      <c r="Q3" s="51" t="inlineStr">
+        <is>
+          <t>Objetivo Estrategico</t>
+        </is>
+      </c>
+      <c r="R3" s="51" t="inlineStr">
+        <is>
+          <t>Accion Estrategica</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" s="44">
       <c r="A4" s="25" t="inlineStr">
@@ -824,6 +864,16 @@
       <c r="P4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="44">
       <c r="A5" s="26" t="inlineStr">
@@ -888,6 +938,16 @@
       <c r="P5" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="44">
       <c r="A6" s="25" t="inlineStr">
@@ -952,6 +1012,16 @@
       <c r="P6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="44">
       <c r="A7" s="26" t="inlineStr">
@@ -1016,6 +1086,16 @@
       <c r="P7" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="44">
       <c r="A8" s="25" t="inlineStr">
@@ -1080,6 +1160,16 @@
       <c r="P8" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="44">
       <c r="A9" s="26" t="inlineStr">
@@ -1144,6 +1234,16 @@
       <c r="P9" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="44">
       <c r="A10" s="25" t="inlineStr">
@@ -1208,6 +1308,16 @@
       <c r="P10" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="44">
       <c r="A11" s="26" t="inlineStr">
@@ -1272,6 +1382,16 @@
       <c r="P11" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="44">
       <c r="A12" s="25" t="inlineStr">
@@ -1336,6 +1456,16 @@
       <c r="P12" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="44">
       <c r="A13" s="26" t="inlineStr">
@@ -1400,6 +1530,16 @@
       <c r="P13" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="44">
       <c r="A14" s="25" t="inlineStr">
@@ -1461,8 +1601,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="44">
@@ -1525,8 +1675,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="44">
@@ -1589,8 +1749,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="44">
@@ -1653,8 +1823,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="44">
@@ -1717,8 +1897,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="44"/>
@@ -2181,6 +2371,16 @@
       <c r="P49" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="44">
       <c r="A50" s="33" t="inlineStr">
@@ -2228,6 +2428,16 @@
       <c r="P50" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="44">
       <c r="A51" s="33" t="inlineStr">
@@ -2275,6 +2485,16 @@
       <c r="P51" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="44">
       <c r="A52" s="33" t="inlineStr">
@@ -2322,6 +2542,16 @@
       <c r="P52" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="44">
       <c r="A53" s="33" t="inlineStr">
@@ -2369,6 +2599,16 @@
       <c r="P53" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Identificar adecuadamente las necesidades de los usuarios para el diseño de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Recopilar requerimientos mediante entrevistas y revisión documental</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="44">
       <c r="A54" s="33" t="inlineStr">
@@ -2416,6 +2656,16 @@
       <c r="P54" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="44">
       <c r="A55" s="33" t="inlineStr">
@@ -2463,6 +2713,16 @@
       <c r="P55" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="44">
       <c r="A56" s="33" t="inlineStr">
@@ -2510,6 +2770,16 @@
       <c r="P56" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="44">
       <c r="A57" s="33" t="inlineStr">
@@ -2557,6 +2827,16 @@
       <c r="P57" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="44">
       <c r="A58" s="33" t="inlineStr">
@@ -2604,6 +2884,16 @@
       <c r="P58" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Analizar integralmente los procesos actuales para identificar oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Levantar y documentar información del proceso actual</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="44">
       <c r="A59" s="33" t="inlineStr">
@@ -2648,8 +2938,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P59" t="n">
+      <c r="P59" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="44">
@@ -2695,8 +2995,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P60" t="n">
+      <c r="P60" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="44">
@@ -2742,8 +3052,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P61" t="n">
+      <c r="P61" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="44">
@@ -2789,8 +3109,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P62" t="n">
+      <c r="P62" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="44">
@@ -2836,8 +3166,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P63" t="n">
+      <c r="P63" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Diseñar servicios interoperables alineados a estándares y necesidades identificadas</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Elaborar el diseño del servicio considerando requerimientos y análisis previo</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="44">
@@ -4442,13 +4782,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.63" customWidth="1" style="44" min="1" max="1"/>
     <col width="34.63" customWidth="1" style="44" min="2" max="2"/>
     <col width="36" customWidth="1" style="44" min="3" max="3"/>
     <col width="12.63" customWidth="1" style="44" min="4" max="7"/>
+    <col width="60" customWidth="1" style="44" min="17" max="17"/>
+    <col width="55" customWidth="1" style="44" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="44">
@@ -4583,6 +4925,16 @@
           <t>Relevancia</t>
         </is>
       </c>
+      <c r="Q3" s="51" t="inlineStr">
+        <is>
+          <t>Objetivo Estrategico</t>
+        </is>
+      </c>
+      <c r="R3" s="51" t="inlineStr">
+        <is>
+          <t>Accion Estrategica</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" s="44">
       <c r="A4" s="25" t="inlineStr">
@@ -4648,6 +5000,16 @@
       <c r="P4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="44">
       <c r="A5" s="26" t="inlineStr">
@@ -4713,6 +5075,16 @@
       <c r="P5" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="44">
       <c r="A6" s="25" t="inlineStr">
@@ -4778,6 +5150,16 @@
       <c r="P6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="44">
       <c r="A7" s="26" t="inlineStr">
@@ -4843,6 +5225,16 @@
       <c r="P7" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="44">
       <c r="A8" s="25" t="inlineStr">
@@ -4908,6 +5300,16 @@
       <c r="P8" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="44">
       <c r="A9" s="26" t="inlineStr">
@@ -4973,6 +5375,16 @@
       <c r="P9" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="44">
       <c r="A10" s="25" t="inlineStr">
@@ -5038,6 +5450,16 @@
       <c r="P10" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="44">
       <c r="A11" s="26" t="inlineStr">
@@ -5103,6 +5525,16 @@
       <c r="P11" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="44">
       <c r="A12" s="25" t="inlineStr">
@@ -5168,6 +5600,16 @@
       <c r="P12" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="44">
       <c r="A13" s="26" t="inlineStr">
@@ -5233,6 +5675,16 @@
       <c r="P13" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="44">
       <c r="A14" s="25" t="inlineStr">
@@ -5295,8 +5747,18 @@
           <t>Amarillo</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="44">
@@ -5360,8 +5822,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="44">
@@ -5425,8 +5897,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="44">
@@ -5490,8 +5972,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="44">
@@ -5555,8 +6047,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="44"/>
@@ -6050,6 +6552,16 @@
       <c r="P50" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="44">
       <c r="A51" s="33" t="inlineStr">
@@ -6098,6 +6610,16 @@
       <c r="P51" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="44">
       <c r="A52" s="33" t="inlineStr">
@@ -6146,6 +6668,16 @@
       <c r="P52" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="44">
       <c r="A53" s="33" t="inlineStr">
@@ -6194,6 +6726,16 @@
       <c r="P53" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="44">
       <c r="A54" s="33" t="inlineStr">
@@ -6242,6 +6784,16 @@
       <c r="P54" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Garantizar la calidad de los servicios de interoperabilidad implementados por la entidad</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Estandarizar el proceso de análisis de solicitudes de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="44">
       <c r="A55" s="33" t="inlineStr">
@@ -6290,6 +6842,16 @@
       <c r="P55" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="44">
       <c r="A56" s="33" t="inlineStr">
@@ -6338,6 +6900,16 @@
       <c r="P56" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="44">
       <c r="A57" s="33" t="inlineStr">
@@ -6386,6 +6958,16 @@
       <c r="P57" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="44">
       <c r="A58" s="33" t="inlineStr">
@@ -6434,6 +7016,16 @@
       <c r="P58" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="44">
       <c r="A59" s="33" t="inlineStr">
@@ -6482,6 +7074,16 @@
       <c r="P59" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Optimizar el tiempo de implementación de los servicios de interoperabilidad</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Estandarizar los procesos de diseño, desarrollo y pruebas de interoperabilidad</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="44">
       <c r="A60" s="33" t="inlineStr">
@@ -6527,8 +7129,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P60" t="n">
+      <c r="P60" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="44">
@@ -6575,8 +7187,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P61" t="n">
+      <c r="P61" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="44">
@@ -6623,8 +7245,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P62" t="n">
+      <c r="P62" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="44">
@@ -6671,8 +7303,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P63" t="n">
+      <c r="P63" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="44">
@@ -6719,8 +7361,18 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="P64" t="n">
+      <c r="P64" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Asegurar la calidad técnica de los servicios de interoperabilidad durante la fase de pruebas</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Fortalecer los procedimientos de pruebas técnicas de interoperabilidad</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="44">
@@ -8341,7 +8993,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="44" min="1" max="1"/>
@@ -8350,6 +9002,8 @@
     <col width="14.25" customWidth="1" style="44" min="4" max="5"/>
     <col width="22.13" customWidth="1" style="44" min="10" max="10"/>
     <col width="20.38" customWidth="1" style="44" min="11" max="11"/>
+    <col width="60" customWidth="1" style="44" min="17" max="17"/>
+    <col width="55" customWidth="1" style="44" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" s="44">
@@ -8484,6 +9138,16 @@
           <t>Relevancia</t>
         </is>
       </c>
+      <c r="Q3" s="51" t="inlineStr">
+        <is>
+          <t>Objetivo Estrategico</t>
+        </is>
+      </c>
+      <c r="R3" s="51" t="inlineStr">
+        <is>
+          <t>Accion Estrategica</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
@@ -8549,6 +9213,16 @@
       <c r="P4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -8614,6 +9288,16 @@
       <c r="P5" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
@@ -8679,6 +9363,16 @@
       <c r="P6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -8744,6 +9438,16 @@
       <c r="P7" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
@@ -8809,6 +9513,16 @@
       <c r="P8" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
@@ -8874,6 +9588,16 @@
       <c r="P9" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -8939,6 +9663,16 @@
       <c r="P10" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
@@ -9004,6 +9738,16 @@
       <c r="P11" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Definir las reglas técnicas y de negocio necesarias para la conexión entre sistemas</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Relevar, documentar y validar los requerimientos de datos a integrar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
@@ -9069,6 +9813,16 @@
       <c r="P12" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
@@ -9134,6 +9888,16 @@
       <c r="P13" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
@@ -9199,6 +9963,16 @@
       <c r="P14" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
@@ -9264,6 +10038,16 @@
       <c r="P15" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
@@ -9329,6 +10113,16 @@
       <c r="P16" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
@@ -9394,6 +10188,16 @@
       <c r="P17" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
@@ -9459,6 +10263,16 @@
       <c r="P18" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="26" t="inlineStr">
@@ -9524,6 +10338,16 @@
       <c r="P19" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Construir los componentes de software que ejecutan la integración entre plataformas</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Codificar, configurar y securizar los servicios de API y middleware</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
@@ -9586,8 +10410,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -9651,8 +10485,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -9716,8 +10560,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -9781,8 +10635,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -9846,8 +10710,18 @@
           <t>Amarillo</t>
         </is>
       </c>
-      <c r="P24" t="n">
+      <c r="P24" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -9911,8 +10785,18 @@
           <t>Amarillo</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -9976,8 +10860,18 @@
           <t>Amarillo</t>
         </is>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -10041,8 +10935,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Validar que los datos se transmiten correctamente y que el sistema cumple los SLA definidos</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Ejecutar pruebas funcionales, de estrés y verificar la estabilidad del servicio integrado</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -10203,13 +11107,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.63" customWidth="1" style="44" min="1" max="1"/>
     <col width="34.63" customWidth="1" style="44" min="2" max="2"/>
     <col width="50.88" customWidth="1" style="44" min="3" max="3"/>
     <col width="12.63" customWidth="1" style="44" min="4" max="7"/>
+    <col width="60" customWidth="1" style="44" min="17" max="17"/>
+    <col width="55" customWidth="1" style="44" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="44">
@@ -10344,6 +11250,16 @@
           <t>Relevancia</t>
         </is>
       </c>
+      <c r="Q3" s="51" t="inlineStr">
+        <is>
+          <t>Objetivo Estrategico</t>
+        </is>
+      </c>
+      <c r="R3" s="51" t="inlineStr">
+        <is>
+          <t>Accion Estrategica</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" s="44">
       <c r="A4" s="25" t="inlineStr">
@@ -10409,6 +11325,16 @@
       <c r="P4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Planificar la orquestación eficiente de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Identificar y analizar los servicios interoperables requeridos</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="44">
       <c r="A5" s="26" t="inlineStr">
@@ -10474,6 +11400,16 @@
       <c r="P5" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Planificar la orquestación eficiente de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Identificar y analizar los servicios interoperables requeridos</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="44">
       <c r="A6" s="25" t="inlineStr">
@@ -10539,6 +11475,16 @@
       <c r="P6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Planificar la orquestación eficiente de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Identificar y analizar los servicios interoperables requeridos</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="44">
       <c r="A7" s="26" t="inlineStr">
@@ -10604,6 +11550,16 @@
       <c r="P7" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Planificar la orquestación eficiente de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Identificar y analizar los servicios interoperables requeridos</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="44">
       <c r="A8" s="25" t="inlineStr">
@@ -10669,6 +11625,16 @@
       <c r="P8" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Planificar la orquestación eficiente de servicios interoperables</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Identificar y analizar los servicios interoperables requeridos</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="44">
       <c r="A9" s="26" t="inlineStr">
@@ -10734,6 +11700,16 @@
       <c r="P9" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Configurar servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Configurar servicios en plataformas de integración</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="44">
       <c r="A10" s="25" t="inlineStr">
@@ -10799,6 +11775,16 @@
       <c r="P10" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Configurar servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Configurar servicios en plataformas de integración</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="44">
       <c r="A11" s="26" t="inlineStr">
@@ -10864,6 +11850,16 @@
       <c r="P11" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Configurar servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Configurar servicios en plataformas de integración</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="44">
       <c r="A12" s="25" t="inlineStr">
@@ -10929,6 +11925,16 @@
       <c r="P12" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Configurar servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Configurar servicios en plataformas de integración</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="44">
       <c r="A13" s="26" t="inlineStr">
@@ -10994,6 +12000,16 @@
       <c r="P13" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Configurar servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Configurar servicios en plataformas de integración</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="44">
       <c r="A14" s="25" t="inlineStr">
@@ -11056,8 +12072,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables configurados</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="44">
@@ -11121,8 +12147,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables configurados</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="44">
@@ -11186,8 +12222,18 @@
           <t>Amarillo</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables configurados</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="44">
@@ -11251,8 +12297,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables configurados</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="44">
@@ -11316,8 +12372,18 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables de manera eficiente</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Ejecutar los servicios interoperables configurados</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="44"/>
